--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCD5BA5-A0B1-4D0A-A426-CC16D0A4702F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8934688-EFD1-46FD-819C-F76E44123478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6343,7 +6343,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E39685E-25FF-4267-9A38-AFE7A3248E53}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E6CA05B-C9BA-4C45-B2F0-AE9D5A9D1FDF}">
   <dimension ref="B3:H229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888F46C8-2177-477F-9A68-05A9CB046D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BF50EC-74B5-4E8F-8403-5D0C4FE445AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4811,7 +4811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BF708E0-1F80-435B-86C0-53443583886F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903A2F4-C133-42C2-9A42-3A44F892D12E}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42BF50EC-74B5-4E8F-8403-5D0C4FE445AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CB3B72-4E26-4FFB-8DCA-D0547E370FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4811,7 +4811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C903A2F4-C133-42C2-9A42-3A44F892D12E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41532496-4042-4EB2-AC94-9B230C80E08A}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CB3B72-4E26-4FFB-8DCA-D0547E370FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D2C2207-6B01-4707-B86D-2D6F5530E976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4811,7 +4811,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41532496-4042-4EB2-AC94-9B230C80E08A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A1E0D41-54EE-4868-85A9-87828601012F}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9467BDC-FCF0-47E4-850E-2BEBAFD78DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C622F4-C5A4-41FC-8257-F4E79DF3F50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4439,7 +4439,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{303D1AB2-7E2E-5946-CA12-B27CE8EEA452}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3A32017-A208-C8FC-508D-E358416D472C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4936,7 +4936,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6A43C9B-F509-4BDB-9955-D119519B3B0C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC7BDF29-DE12-4966-AD60-D0D85791EA60}">
   <dimension ref="A1:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34D687D7-9A2C-41BD-AE1C-5FEBC9494E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD8884D-587E-4943-A37E-FF88ACC4A6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E623A5E4-D21E-4C39-8A10-F83F00D042AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85AEC3D-4064-4B23-ABE8-A8EB5EB13AA4}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD8884D-587E-4943-A37E-FF88ACC4A6FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEFFF09-F218-497B-AF87-6FFB76E5B214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D85AEC3D-4064-4B23-ABE8-A8EB5EB13AA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172CA00D-3818-4CF6-94B5-B8BE34BA8AB7}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SysSettings.xlsx
+++ b/VerveStacks_POL_grids_kan/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEFFF09-F218-497B-AF87-6FFB76E5B214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D9B8E93-FC04-4BE2-84F5-DD9C271A09C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4823,7 +4823,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{172CA00D-3818-4CF6-94B5-B8BE34BA8AB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CD76566-6BE4-497A-9094-937D6EF2FA92}">
   <dimension ref="B3:I229"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
